--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.81755384745369</v>
+        <v>8.745352500211226</v>
       </c>
       <c r="D2" t="n">
-        <v>54.91998607824027</v>
+        <v>8.924497737714045</v>
       </c>
       <c r="E2" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F2" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.51295267116585</v>
+        <v>7.070854809064451</v>
       </c>
       <c r="D3" t="n">
-        <v>44.30911812452344</v>
+        <v>7.200231695235058</v>
       </c>
       <c r="E3" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F3" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.17521821125715</v>
+        <v>5.878472959329287</v>
       </c>
       <c r="D4" t="n">
-        <v>34.63327466968828</v>
+        <v>5.627907133824347</v>
       </c>
       <c r="E4" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F4" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.62326859323917</v>
+        <v>2.213781146401365</v>
       </c>
       <c r="D5" t="n">
-        <v>13.38484459148662</v>
+        <v>2.175037246116576</v>
       </c>
       <c r="E5" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F5" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.39369966806882</v>
+        <v>3.476476196061183</v>
       </c>
       <c r="D6" t="n">
-        <v>45.7959786229792</v>
+        <v>7.44184652623412</v>
       </c>
       <c r="E6" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F6" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.17946990042111</v>
+        <v>6.366663858818431</v>
       </c>
       <c r="D7" t="n">
-        <v>47.48850517296442</v>
+        <v>7.716882090606718</v>
       </c>
       <c r="E7" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F7" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.3658476144772</v>
+        <v>6.071950237352546</v>
       </c>
       <c r="D8" t="n">
-        <v>36.50357496296051</v>
+        <v>5.931830931481082</v>
       </c>
       <c r="E8" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F8" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.6459678265398</v>
+        <v>5.629969771812718</v>
       </c>
       <c r="D9" t="n">
-        <v>33.1640458888762</v>
+        <v>5.389157456942382</v>
       </c>
       <c r="E9" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F9" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.6210659975415</v>
+        <v>7.088423224600494</v>
       </c>
       <c r="D10" t="n">
-        <v>21.00932827100123</v>
+        <v>3.4140158440377</v>
       </c>
       <c r="E10" t="n">
-        <v>11.35215100157736</v>
+        <v>1.844724537756321</v>
       </c>
       <c r="F10" t="n">
-        <v>12.45217545291228</v>
+        <v>2.023478511098245</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
